--- a/02_DIA_inicio_2026_analisis_assets/rbd_25173_esc-basica-municipal-risopatron_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_25173_esc-basica-municipal-risopatron_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F27EBFC7-A6C7-42A2-B713-822F68096F3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41CADB08-60D7-4CFB-A3DA-0526338C913E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5873994A-8231-42CF-AA0F-38FD87758A75}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48CE841B-B9FB-43B5-A3DE-FD5E6D228F81}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6491D74F-EA86-46E2-91DE-11F2B6ED0E1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6891F9E-2A91-45F7-9505-36E019737D5B}"/>
 </file>